--- a/storage/downloads/Construction_Calculator_Pro_INDIA_v2.xlsx
+++ b/storage/downloads/Construction_Calculator_Pro_INDIA_v2.xlsx
@@ -9802,7 +9802,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="48" customHeight="1" s="35">
       <c r="A4" s="30" t="inlineStr">
         <is>
@@ -9895,7 +9894,7 @@
       </c>
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>Published by Thinktools (thinktools.in). Customer Support: orders@thinktools.in. Licensed for single-user personal and business planning. All sales final; replacement support available.</t>
+          <t>Published by Thinktools (thinktools.in). Customer Support: support@thinktools.in. Licensed for single-user personal and business planning. All sales final; replacement support available.</t>
         </is>
       </c>
     </row>
